--- a/BOM/CAN_Sensor_PCB.xlsx
+++ b/BOM/CAN_Sensor_PCB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\CAN_Sensor_PCB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6601EC6E-A53F-47E9-9E22-280C7E51550A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE1DC63-13AD-41EF-A59B-47B622A7C29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
   <si>
     <t>Reference</t>
   </si>
@@ -28,24 +28,21 @@
     <t>Value</t>
   </si>
   <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Replacement</t>
+  </si>
+  <si>
+    <t>Description P/N</t>
+  </si>
+  <si>
     <t>Footprint</t>
   </si>
   <si>
     <t>Qty</t>
   </si>
   <si>
-    <t>Description P/N</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Replacement</t>
-  </si>
-  <si>
     <t>DNP</t>
   </si>
   <si>
@@ -55,6 +52,9 @@
     <t>100n</t>
   </si>
   <si>
+    <t>Capacitor SMD 10V+</t>
+  </si>
+  <si>
     <t>Capacitor_SMD:C_0805_2012Metric_Pad1.18x1.45mm_HandSolder</t>
   </si>
   <si>
@@ -88,6 +88,9 @@
     <t>10u</t>
   </si>
   <si>
+    <t>Capacitor SMD 50V+</t>
+  </si>
+  <si>
     <t>Capacitor_SMD:C_1210_3225Metric_Pad1.33x2.70mm_HandSolder</t>
   </si>
   <si>
@@ -97,6 +100,12 @@
     <t>100u</t>
   </si>
   <si>
+    <t>293D107X96R3B2TE3</t>
+  </si>
+  <si>
+    <t>Tantalum Capacitor</t>
+  </si>
+  <si>
     <t>Capacitor_Tantalum_SMD:CP_EIA-3528-21_Kemet-B_HandSolder</t>
   </si>
   <si>
@@ -112,60 +121,60 @@
     <t>~</t>
   </si>
   <si>
+    <t>SIT65HVD232DR</t>
+  </si>
+  <si>
+    <t>CAN interface</t>
+  </si>
+  <si>
     <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
   </si>
   <si>
-    <t>CAN interface</t>
-  </si>
-  <si>
-    <t>SIT65HVD232DR</t>
-  </si>
-  <si>
     <t>D2</t>
   </si>
   <si>
+    <t>PESD2CAN</t>
+  </si>
+  <si>
+    <t>Dual Line CAN Bus Protector, 24Vrwm</t>
+  </si>
+  <si>
     <t>Package_TO_SOT_SMD:SOT-23</t>
   </si>
   <si>
-    <t>Dual Line CAN Bus Protector, 24Vrwm</t>
-  </si>
-  <si>
-    <t>PESD2CAN</t>
-  </si>
-  <si>
     <t>D3</t>
   </si>
   <si>
+    <t>BAS416</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
     <t>Diode_SMD:D_SOD-323_HandSoldering</t>
   </si>
   <si>
-    <t>Diode</t>
-  </si>
-  <si>
-    <t>BAS416</t>
-  </si>
-  <si>
     <t>D4</t>
   </si>
   <si>
+    <t>FYLS-0805UYC</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
     <t>LED_SMD:LED_0805_2012Metric</t>
   </si>
   <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>FYLS-0805UYC</t>
-  </si>
-  <si>
     <t>D5</t>
   </si>
   <si>
+    <t>MBRA320</t>
+  </si>
+  <si>
     <t>Diode_SMD:D_SMA</t>
   </si>
   <si>
-    <t>MBRA320</t>
-  </si>
-  <si>
     <t>D6</t>
   </si>
   <si>
@@ -178,72 +187,57 @@
     <t>FYLS-0805PGC</t>
   </si>
   <si>
-    <t>J1</t>
+    <t>J1,J3</t>
+  </si>
+  <si>
+    <t>Connector</t>
   </si>
   <si>
     <t>Wire_my:Wire_1.5mm</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
+    <t>PLS-4</t>
+  </si>
+  <si>
+    <t>DS-1021-1x4</t>
+  </si>
+  <si>
     <t>Connector_PinHeader_2.54mm:PinHeader_1x04_P2.54mm_Vertical</t>
   </si>
   <si>
-    <t>Connector</t>
-  </si>
-  <si>
-    <t>PLS-4</t>
-  </si>
-  <si>
-    <t>SWD</t>
-  </si>
-  <si>
-    <t>DS-1021-1x4</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>J4</t>
+    <t>J4,J5</t>
   </si>
   <si>
     <t>Wire_my:Wire_1.5mm x 4</t>
   </si>
   <si>
-    <t>PT1</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>PT2</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
     <t>47u</t>
   </si>
   <si>
+    <t>NLC453232T-470K-PF</t>
+  </si>
+  <si>
+    <t>Inductor SMD</t>
+  </si>
+  <si>
     <t>Inductor_SMD:L_1812_4532Metric_Pad1.30x3.40mm_HandSolder</t>
   </si>
   <si>
-    <t>NLC453232T-470K-PF</t>
-  </si>
-  <si>
-    <t>R1,R2,R5,R6,R8,R10,R11,R12,R15,R16,R17,R18</t>
+    <t>R1,R2,R5,R6</t>
   </si>
   <si>
     <t>1k</t>
   </si>
   <si>
+    <t>Resistor SMD</t>
+  </si>
+  <si>
     <t>Resistor_SMD:R_0805_2012Metric_Pad1.20x1.40mm_HandSolder</t>
   </si>
   <si>
@@ -256,59 +250,100 @@
     <t>R7,R9</t>
   </si>
   <si>
+    <t>16k</t>
+  </si>
+  <si>
+    <t>Resistor SMD 0.1%</t>
+  </si>
+  <si>
+    <t>R8,R10,R17,R18</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>R11,R12,R15,R16</t>
+  </si>
+  <si>
+    <t>100k</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
+    <t>APM32F405RGT6</t>
+  </si>
+  <si>
+    <t>uController</t>
+  </si>
+  <si>
     <t>Package_QFP:LQFP-64_10x10mm_P0.5mm</t>
   </si>
   <si>
-    <t>APM32F405RGT6</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
     <t>LM2594HVM-3.3</t>
   </si>
   <si>
+    <t>DCDC</t>
+  </si>
+  <si>
     <t>U5</t>
   </si>
   <si>
+    <t>LM158DR</t>
+  </si>
+  <si>
+    <t>OpAmp</t>
+  </si>
+  <si>
     <t>Package_SO:SO-8_3.9x4.9mm_P1.27mm</t>
   </si>
   <si>
-    <t>LM158DR</t>
-  </si>
-  <si>
     <t>Y1</t>
   </si>
   <si>
+    <t>X322516MOB4SI</t>
+  </si>
+  <si>
+    <t>Crystal</t>
+  </si>
+  <si>
     <t>Crystal:Crystal_SMD_SeikoEpson_FA238-4Pin_3.2x2.5mm</t>
-  </si>
-  <si>
-    <t>Crystal</t>
-  </si>
-  <si>
-    <t>X322516MOB4SI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -321,16 +356,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -338,9 +373,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -647,659 +685,655 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" customWidth="1"/>
-    <col min="5" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1">
+      <c r="G2" s="1">
         <v>9</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1">
+      <c r="G3" s="1">
         <v>7</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1">
+      <c r="G4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
+      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1">
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
         <v>3</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="1">
+      <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="B22" s="1">
+        <v>120</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="F22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="1">
+        <v>750</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="1">
-        <v>12</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="1">
-        <v>120</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="1">
-        <v>750</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4</v>
+      </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="1">
-        <v>160</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4</v>
+      </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>90</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
